--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488125_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488125_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0052</v>
+        <v>5.9871</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7003</v>
+        <v>6.9284</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6951000000000001</v>
+        <v>-0.9413</v>
       </c>
       <c r="G2" t="n">
         <v>4.1827</v>
@@ -610,13 +610,13 @@
         <v>2.9646</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3604</v>
+        <v>0.3423</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1341</v>
+        <v>0.3622</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2263</v>
+        <v>-0.0199</v>
       </c>
       <c r="V2" t="n">
         <v>2.2033</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6717</v>
+        <v>2.3167</v>
       </c>
       <c r="E3" t="n">
-        <v>2.076</v>
+        <v>1.5979</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5957</v>
+        <v>0.7188</v>
       </c>
       <c r="G3" t="n">
         <v>2.5795</v>
@@ -688,13 +688,13 @@
         <v>1.1117</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1478</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1291</v>
+        <v>0.651</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0186</v>
+        <v>0.1418</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3144</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1746</v>
+        <v>1.3568</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.2501</v>
+        <v>-0.9448</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4247</v>
+        <v>2.3016</v>
       </c>
       <c r="G4" t="n">
         <v>-1.6697</v>
@@ -766,13 +766,13 @@
         <v>2.4087</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1032</v>
+        <v>0.2854</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4539</v>
+        <v>-0.1486</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5571</v>
+        <v>0.434</v>
       </c>
       <c r="V4" t="n">
         <v>1.2589</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. PERRY II</t>
+          <t>H. SANTOS PARRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3786</v>
+        <v>-1.1404</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2896</v>
+        <v>-2.1996</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.089</v>
+        <v>1.0593</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.5411</v>
+        <v>-4.0488</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.831</v>
+        <v>-2.3653</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.7101</v>
+        <v>-1.6835</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.3052</v>
+        <v>-2.2708</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0289</v>
+        <v>-1.0481</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.334</v>
+        <v>-1.2228</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.2359</v>
+        <v>-1.778</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.8598</v>
+        <v>-1.3173</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3761</v>
+        <v>-0.4607</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6676</v>
+        <v>2.4087</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.5205</v>
+        <v>2.4087</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4949</v>
+        <v>-0.1303</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0199</v>
+        <v>0.0712</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5148</v>
+        <v>-0.2015</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="W6" t="n">
-        <v>1.8883</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.8883</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. SANTOS PARRA</t>
+          <t>T. PERRY II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.705</v>
+        <v>-1.1417</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.4934</v>
+        <v>-0.9296</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7884</v>
+        <v>-0.2121</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.0488</v>
+        <v>-3.5411</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.3653</v>
+        <v>-1.831</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.6835</v>
+        <v>-1.7101</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.2708</v>
+        <v>-1.3052</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.0481</v>
+        <v>0.0289</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2228</v>
+        <v>-1.334</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.778</v>
+        <v>-2.2359</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3173</v>
+        <v>-1.8598</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4607</v>
+        <v>-0.3761</v>
       </c>
       <c r="P7" t="n">
-        <v>2.4087</v>
+        <v>1.6676</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4087</v>
+        <v>3.5205</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6949</v>
+        <v>0.7318</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2226</v>
+        <v>0.3401</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4723</v>
+        <v>0.3917</v>
       </c>
       <c r="V7" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.8883</v>
       </c>
       <c r="X7" t="n">
-        <v>0.63</v>
+        <v>-1.8883</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.4693</v>
+        <v>-2.717</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5928</v>
+        <v>0.061</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.8764</v>
+        <v>-2.7779</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4448</v>
@@ -1078,13 +1078,13 @@
         <v>1.297</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5449000000000001</v>
+        <v>0.2074</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5596</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0147</v>
+        <v>0.1131</v>
       </c>
       <c r="V8" t="n">
         <v>-3.7766</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. PARRA RIVERA</t>
+          <t>J. SANCHEZ BARQUIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.4257</v>
+        <v>-3.9908</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2678</v>
+        <v>-2.9059</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1579</v>
+        <v>-1.0849</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4939</v>
+        <v>-1.8788</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1021</v>
+        <v>-0.0417</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.596</v>
+        <v>-1.8371</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2842</v>
+        <v>0.044</v>
       </c>
       <c r="K9" t="n">
-        <v>1.55</v>
+        <v>1.2668</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.8342</v>
+        <v>-1.2228</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2097</v>
+        <v>-1.9228</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4478</v>
+        <v>-1.3085</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2381</v>
+        <v>-0.6143</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.594</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.6322</v>
+        <v>-2.7793</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0382</v>
+        <v>2.7793</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2361</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0197</v>
+        <v>-0.1706</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2164</v>
+        <v>-0.3681</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5738</v>
+        <v>-1.5733</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.2027</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. SANCHEZ BARQUIN</t>
+          <t>A. PARRA RIVERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.6583</v>
+        <v>-4.6352</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4503</v>
+        <v>-3.3542</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.208</v>
+        <v>-1.281</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8788</v>
+        <v>-1.4939</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0417</v>
+        <v>0.1021</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8371</v>
+        <v>-1.596</v>
       </c>
       <c r="J10" t="n">
-        <v>0.044</v>
+        <v>-0.2842</v>
       </c>
       <c r="K10" t="n">
-        <v>1.2668</v>
+        <v>1.55</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2228</v>
+        <v>-1.8342</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9228</v>
+        <v>-1.2097</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3085</v>
+        <v>-1.4478</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6143</v>
+        <v>0.2381</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-2.594</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.7793</v>
+        <v>-4.6322</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7793</v>
+        <v>2.0382</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2062</v>
+        <v>1.0265</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.715</v>
+        <v>0.9333</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4912</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5733</v>
+        <v>-1.5738</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5733</v>
+        <v>-2.2027</v>
       </c>
     </row>
     <row r="11">
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.463299999999999</v>
+        <v>-3.642400000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.245599999999997</v>
+        <v>-1.424700000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2176</v>
+        <v>-2.2175</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.992800000000001</v>
+        <v>-5.992799999999999</v>
       </c>
       <c r="H11" t="n">
         <v>1.0735</v>
@@ -1285,7 +1285,7 @@
         <v>-7.0665</v>
       </c>
       <c r="J11" t="n">
-        <v>4.9548</v>
+        <v>4.954800000000001</v>
       </c>
       <c r="K11" t="n">
         <v>10.1406</v>
@@ -1303,7 +1303,7 @@
         <v>-1.8807</v>
       </c>
       <c r="P11" t="n">
-        <v>2.7794</v>
+        <v>2.779399999999999</v>
       </c>
       <c r="Q11" t="n">
         <v>-15.7494</v>
@@ -1312,10 +1312,10 @@
         <v>18.5287</v>
       </c>
       <c r="S11" t="n">
-        <v>1.8964</v>
+        <v>2.7171</v>
       </c>
       <c r="T11" t="n">
-        <v>1.311900000000001</v>
+        <v>2.1328</v>
       </c>
       <c r="U11" t="n">
         <v>0.5844</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.851</v>
+        <v>7.1172</v>
       </c>
       <c r="E12" t="n">
-        <v>4.0325</v>
+        <v>4.816</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8185</v>
+        <v>2.3012</v>
       </c>
       <c r="G12" t="n">
         <v>0.512</v>
@@ -1390,13 +1390,13 @@
         <v>2.0382</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.158</v>
+        <v>0.1082</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7113</v>
+        <v>0.0721</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4467</v>
+        <v>0.036</v>
       </c>
       <c r="V12" t="n">
         <v>7.2381</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. MENDEZ CARRION</t>
+          <t>J. WOJCIK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.6077</v>
+        <v>2.9969</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1086</v>
+        <v>2.5092</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4992</v>
+        <v>0.4878</v>
       </c>
       <c r="G13" t="n">
-        <v>4.4502</v>
+        <v>2.8002</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3413</v>
+        <v>0.8264</v>
       </c>
       <c r="I13" t="n">
-        <v>4.1089</v>
+        <v>1.9738</v>
       </c>
       <c r="J13" t="n">
-        <v>4.545</v>
+        <v>4.1625</v>
       </c>
       <c r="K13" t="n">
-        <v>1.2581</v>
+        <v>2.1814</v>
       </c>
       <c r="L13" t="n">
-        <v>3.2869</v>
+        <v>1.9812</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0948</v>
+        <v>-1.3624</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9167999999999999</v>
+        <v>-1.355</v>
       </c>
       <c r="O13" t="n">
-        <v>0.822</v>
+        <v>-0.0074</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.7793</v>
+        <v>-1.8529</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2234</v>
+        <v>2.4087</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9717</v>
+        <v>-0.3591</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0284</v>
+        <v>-0.4299</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0567</v>
+        <v>0.0709</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2583</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.3144</v>
+        <v>0.6294</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.5727</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. WOJCIK</t>
+          <t>A. MENDEZ CARRION</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6368</v>
+        <v>2.7579</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6071</v>
+        <v>2.3251</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0297</v>
+        <v>0.4328</v>
       </c>
       <c r="G14" t="n">
-        <v>2.8002</v>
+        <v>4.4502</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8264</v>
+        <v>0.3413</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9738</v>
+        <v>4.1089</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1625</v>
+        <v>4.545</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1814</v>
+        <v>1.2581</v>
       </c>
       <c r="L14" t="n">
-        <v>1.9812</v>
+        <v>3.2869</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3624</v>
+        <v>-0.0948</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.355</v>
+        <v>-0.9167999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0074</v>
+        <v>0.822</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5558999999999999</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.8529</v>
+        <v>-2.7793</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4087</v>
+        <v>2.2234</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7193000000000001</v>
+        <v>0.1219</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.332</v>
+        <v>0.245</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3873</v>
+        <v>-0.1231</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-1.2583</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6294</v>
+        <v>0.3144</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6294</v>
+        <v>-1.5727</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4593</v>
+        <v>1.8963</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1825</v>
+        <v>-0.405</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2767</v>
+        <v>2.3013</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1917</v>
@@ -1624,13 +1624,13 @@
         <v>1.297</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6504</v>
+        <v>1.0875</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4114</v>
+        <v>0.8239</v>
       </c>
       <c r="U15" t="n">
-        <v>0.239</v>
+        <v>0.2636</v>
       </c>
       <c r="V15" t="n">
         <v>0.63</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. ALOGO EVUNA</t>
+          <t>J. PAREDES BERMEJO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1476</v>
+        <v>0.0654</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7747000000000001</v>
+        <v>-0.0638</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9223</v>
+        <v>0.1292</v>
       </c>
       <c r="G17" t="n">
-        <v>2.753</v>
+        <v>0.498</v>
       </c>
       <c r="H17" t="n">
-        <v>2.6085</v>
+        <v>0.6331</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1445</v>
+        <v>-0.1351</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6083</v>
+        <v>1.1707</v>
       </c>
       <c r="K17" t="n">
-        <v>4.1782</v>
+        <v>1.7821</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5699</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8552</v>
+        <v>-0.6727</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5697</v>
+        <v>-1.149</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7144</v>
+        <v>0.4763</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.4087</v>
+        <v>0.1853</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.6322</v>
+        <v>-0.9264</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2234</v>
+        <v>1.1117</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1375</v>
+        <v>0.0115</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5397</v>
+        <v>-0.3081</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4022</v>
+        <v>0.3196</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6294</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.8883</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. PAREDES BERMEJO</t>
+          <t>A. MEJIA BERIGUETE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.359</v>
+        <v>-0.3159</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3576</v>
+        <v>-1.2056</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0014</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>0.498</v>
+        <v>0.3513</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6331</v>
+        <v>1.7966</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1351</v>
+        <v>-1.4453</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1707</v>
+        <v>1.2759</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7821</v>
+        <v>3.1516</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-1.8756</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6727</v>
+        <v>-0.9247</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.149</v>
+        <v>-1.355</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4763</v>
+        <v>0.4303</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1853</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1117</v>
+        <v>2.0382</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4129</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6019</v>
+        <v>-0.3311</v>
       </c>
       <c r="U18" t="n">
-        <v>0.189</v>
+        <v>-0.2239</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6294</v>
+        <v>0.6289</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5474</v>
+        <v>-0.5228</v>
       </c>
       <c r="E19" t="n">
         <v>-0.7955</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2481</v>
+        <v>0.2728</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4544</v>
@@ -1936,13 +1936,13 @@
         <v>0.1853</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2783</v>
+        <v>-0.2537</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1641</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1142</v>
+        <v>-0.0895</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. MEJIA BERIGUETE</t>
+          <t>R. ALOGO EVUNA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3622</v>
+        <v>-0.8749</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6952</v>
+        <v>0.0892</v>
       </c>
       <c r="F20" t="n">
-        <v>0.333</v>
+        <v>-0.964</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3513</v>
+        <v>2.753</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7966</v>
+        <v>2.6085</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4453</v>
+        <v>0.1445</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2759</v>
+        <v>3.6083</v>
       </c>
       <c r="K20" t="n">
-        <v>3.1516</v>
+        <v>4.1782</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.8756</v>
+        <v>-0.5699</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9247</v>
+        <v>-0.8552</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.355</v>
+        <v>-1.5697</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4303</v>
+        <v>0.7144</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7411</v>
+        <v>-2.4087</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.7793</v>
+        <v>-4.6322</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0382</v>
+        <v>2.2234</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6012</v>
+        <v>-0.5898</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8207</v>
+        <v>-0.1458</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7805</v>
+        <v>-0.444</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6289</v>
+        <v>-0.6294</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6289</v>
+        <v>1.2589</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.8883</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6128</v>
+        <v>-1.6872</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7337</v>
+        <v>-1.6358</v>
       </c>
       <c r="F21" t="n">
-        <v>0.121</v>
+        <v>-0.0514</v>
       </c>
       <c r="G21" t="n">
         <v>-0.748</v>
@@ -2092,13 +2092,13 @@
         <v>0.3706</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3089</v>
+        <v>-0.3833</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2189</v>
+        <v>-0.1209</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.09</v>
+        <v>-0.2624</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8768</v>
+        <v>-2.7291</v>
       </c>
       <c r="E22" t="n">
         <v>-2.0498</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-0.6793</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8685</v>
@@ -2170,13 +2170,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0102</v>
+        <v>0.1579</v>
       </c>
       <c r="T22" t="n">
         <v>0.1057</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0955</v>
+        <v>0.0522</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5744</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5079</v>
+        <v>-3.257</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.178</v>
+        <v>-1.6884</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3299</v>
+        <v>-1.5686</v>
       </c>
       <c r="G23" t="n">
         <v>-2.4313</v>
@@ -2248,13 +2248,13 @@
         <v>1.297</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1878</v>
+        <v>0.0631</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8207</v>
+        <v>-0.3311</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6329</v>
+        <v>0.3942</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2594</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>4.463200000000002</v>
+        <v>5.7689</v>
       </c>
       <c r="E24" t="n">
-        <v>2.2177</v>
+        <v>2.217700000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>2.2455</v>
+        <v>3.551399999999999</v>
       </c>
       <c r="G24" t="n">
         <v>5.992899999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.073500000000001</v>
+        <v>-1.0735</v>
       </c>
       <c r="I24" t="n">
         <v>7.066500000000001</v>
@@ -2326,16 +2326,16 @@
         <v>15.7494</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.8966</v>
+        <v>-0.5907</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5844</v>
+        <v>-0.5842999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.3122</v>
+        <v>-0.006400000000000017</v>
       </c>
       <c r="V24" t="n">
-        <v>3.1461</v>
+        <v>3.146100000000001</v>
       </c>
       <c r="W24" t="n">
         <v>10.3831</v>
